--- a/www/download/COUNTRY.RUS.rpPE.xlsx
+++ b/www/download/COUNTRY.RUS.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>Rússia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>4.55830055232312</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>5.11430472219677</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>5.77834273816551</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>7.8149424347516</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>24.5519274245525</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>28.1293966851355</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>29.1545193075099</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>31.2597692412854</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>30.6748461871486</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>28.8101402341572</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>28.2805421596531</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>27.1739125987614</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>25.5623721631117</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>24.7644282612643</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>31.6246524416827</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>75.064</t>
+          <t>8.83216618699862</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>72.952</t>
+          <t>7.23917789824051</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.752</t>
+          <t>6.71336790256632</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.679</t>
+          <t>8.80988631007028</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>72.536</t>
+          <t>17.5080869821024</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>73.726</t>
+          <t>13.3838529372168</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>74.727</t>
+          <t>10.3789529801647</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>74.928</t>
+          <t>8.57181094430946</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>75.796</t>
+          <t>7.02908399347586</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>76.274</t>
+          <t>5.70684891505464</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>76.903</t>
+          <t>4.52691138656945</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>77.376</t>
+          <t>3.41722903001717</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>78.352</t>
+          <t>2.64522004220327</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>78.688</t>
+          <t>1.73034060312605</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>75.717</t>
+          <t>2.30009918911308</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>64.261</t>
+          <t>6.6826355490782</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>62.37</t>
+          <t>5.20846187779654</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>62.201</t>
+          <t>5.05609594056961</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59.854</t>
+          <t>6.5120921522525</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>60.787</t>
+          <t>12.4228529487935</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>61.691</t>
+          <t>9.29264942490199</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>62.298</t>
+          <t>7.61377631651906</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>62.039</t>
+          <t>6.5180913156077</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>62.159</t>
+          <t>5.49239195438128</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>62.522</t>
+          <t>4.38841450557353</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>63.551</t>
+          <t>3.64852790437347</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>63.928</t>
+          <t>2.8023076649221</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>64.757</t>
+          <t>2.22400962646751</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>64.97</t>
+          <t>1.56140380022453</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>62.523</t>
+          <t>2.16059716176307</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>147480.245</t>
+          <t>3.11960532629767</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>145736.147</t>
+          <t>2.36641822557063</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>143947.993</t>
+          <t>2.312547774418</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>139814.023</t>
+          <t>2.90850134133725</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>140635.672</t>
+          <t>5.54750312398172</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>142066.304</t>
+          <t>3.92069157618924</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>143725.423</t>
+          <t>3.21043886982432</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>144652.032</t>
+          <t>2.57030634815664</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>145979.323</t>
+          <t>2.43588169021337</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>147237.004</t>
+          <t>1.794355231195</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>147629.163</t>
+          <t>1.40702994798937</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>148512.153</t>
+          <t>1.03245143176387</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>150394.471</t>
+          <t>0.839210144855255</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>151060.45</t>
+          <t>0.527845870939245</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>147091.434</t>
+          <t>0.907845535416994</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>120664.857</t>
+          <t>697457407740.665</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>119341.921</t>
+          <t>685099594682.698</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>118011.108</t>
+          <t>646009994493.726</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>113027.024</t>
+          <t>639755017295.614</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>113179.63</t>
+          <t>611208761444.626</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>113940.227</t>
+          <t>654011619695.408</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>114153.881</t>
+          <t>674253179641.755</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>113749.879</t>
+          <t>652181574645.847</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>112966.14</t>
+          <t>596907593997.419</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>114564.731</t>
+          <t>626356353126.73</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>116454.544</t>
+          <t>611759612594.587</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>117538.537</t>
+          <t>585352967048.226</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>119035.202</t>
+          <t>567114858515.015</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>111132.001</t>
+          <t>544534114543.604</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>108212.079</t>
+          <t>535024932377.459</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>52016336930.0046</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>62245619616.4512</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>63873496380.183</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>51566752208.4561</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>29490075260.8925</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>40138691390.6187</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>49029692268.2832</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>56269506594.011</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>59463904644.7534</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>76662074316.3116</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>89673009991.8763</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>107953272404.597</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>121843212642.434</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>138507317347.76</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>110954572811.513</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>39241672.0366103</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>29889968.3234935</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>27740911.9759806</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>36207234.0335805</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>72.08</t>
+          <t>61883589.3773157</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>51737527.6883285</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>71.57</t>
+          <t>43616451.635244</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>38052294.3501356</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>29479672.2851472</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>71.52</t>
+          <t>23256425.7972114</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>71.22</t>
+          <t>18506999.8686834</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>71.22</t>
+          <t>14003941.9284039</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>71.22</t>
+          <t>10287118.0624354</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>71.22</t>
+          <t>7803168.95038687</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>71.22</t>
+          <t>9970513.38147623</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>1441672.09001595</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>1386737.93281619</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>1300743.72927882</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>1232262.52878835</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>1280472.24225113</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>1310130.88841617</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>1267057.79369714</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>1281486.96578965</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>1352004.96082989</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>1487442.89152864</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>1573027.94474188</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>1629204.04010511</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>1812752.55553181</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>1953712.62315921</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>1745199.53432436</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>2301208.50563672</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>2286646.91422836</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>2109534.96003753</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>1982013.09677964</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>1917027.04632992</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>1995670.79249877</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>1984654.27973628</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>1970947.6991161</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>2091383.07277281</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>2279740.41292603</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>2412546.23669959</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>2454626.14750163</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>2811026.37949783</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>3066809.69092976</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>2775706.73194178</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>75.42</t>
+          <t>6.89281100677284</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>75.16</t>
+          <t>5.43542218679376</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.02</t>
+          <t>5.22921463960077</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>6.77055709179668</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>74.54</t>
+          <t>13.024749928656</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>9.82339386858012</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>74.04</t>
+          <t>7.99523470073347</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>6.80478968307779</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>5.7361947744024</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>73.11</t>
+          <t>4.61693398354901</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>3.7932537711522</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>2.89984328894402</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>2.28664080076017</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>73.04</t>
+          <t>1.56985475485703</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>2.15591366190698</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>60322.0338121859</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>79310.3707332916</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>80742.2991077465</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>73431.3567097784</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>38895.9306411891</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>51416.9833576182</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>59016.8468249524</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>64307.2620314196</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>76553.8288102808</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>99432.3443358154</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>119651.786736151</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>145357.078662039</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>194949.386282253</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>251866.957028499</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>226246.802231757</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.55830055232312</t>
+          <t>809.456064185413</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.11430472219677</t>
+          <t>998.003761790848</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5.77834273816551</t>
+          <t>1026.88939582308</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7.8149424347516</t>
+          <t>861.546302785114</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>24.5519274245525</t>
+          <t>485.135132140384</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>28.1293966851355</t>
+          <t>650.639887948473</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>29.1545193075099</t>
+          <t>787.021327908193</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>31.2597692412854</t>
+          <t>906.995700997279</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30.6748461871486</t>
+          <t>956.634937857567</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>28.8101402341572</t>
+          <t>1226.15507169311</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>28.2805421596531</t>
+          <t>1411.03258615422</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>27.1739125987614</t>
+          <t>1688.67922976091</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>25.5623721631117</t>
+          <t>1881.54491959282</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>24.7644282612643</t>
+          <t>2131.85643455478</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>31.6246524416827</t>
+          <t>1774.60877691789</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>-16586614116.0961</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>-10372998823.8578</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>-13257950276.5246</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>-27632617117.643</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>-50586067889.8209</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>-35883587324.2795</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>-23479923670.0483</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>-18528258656.5318</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1822689007.68799</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>28369979380.4273</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>52804756506.0224</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>55997933603.1727</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>77610756656.9674</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>95375471354.5148</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>95564841009.6587</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>-21107015805.7257</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>-16193645477.5315</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>-18509583506.2516</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>-34450189842.0936</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>-56899313263.0074</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>-44849826446.1023</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>-32519156581.2993</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>-28092339295.3749</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-7401824388.45312</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>17035512761.0605</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>40249828956.0287</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>40091897262.4229</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>61909494333.9327</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.843</t>
+          <t>76443576649.608</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>81636226512.5798</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>4520401689.62959</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>5820646653.67375</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>5251633229.72703</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>6817572724.4506</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>6313245373.18653</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>8966239121.82285</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>9039232911.25102</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>9564080638.84309</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>9224513396.14111</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>11334466619.3668</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>12554927549.9937</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.796</t>
+          <t>15906036340.7498</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.368</t>
+          <t>15701262323.0347</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.122</t>
+          <t>18931894704.9068</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.751</t>
+          <t>13928614497.0788</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>6388.88373290165</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>6422.57555113245</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.749</t>
+          <t>6396.71445771189</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>6694.69473301807</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>6803.89890987435</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>7042.13177387516</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>7079.44155901711</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>7078.91068973947</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>6444.07926940691</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>6887.23209129401</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>6763.43726480235</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.701</t>
+          <t>6585.58436136223</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.259</t>
+          <t>6183.96230119677</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.892</t>
+          <t>5478.56139501314</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.186</t>
+          <t>5600.51208361522</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>8004.47444282512</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>7970.33797000993</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>7909.02582045351</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>8318.89417394466</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>8359.66481332036</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>8666.61992759721</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>8703.161271089</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>8659.72117756097</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>7877.93789533619</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>8372.44489589757</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>8173.87717221118</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>7954.95574461465</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>7441.15595064741</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>7082.0832925471</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>7197.76123674024</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>883.22</t>
+          <t>82173.1297216709</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>723.92</t>
+          <t>89997.7902277408</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>671.34</t>
+          <t>87131.3766871262</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>880.99</t>
+          <t>91285.0577158808</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1750.81</t>
+          <t>73610.5996215525</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1338.39</t>
+          <t>98756.914410536</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1037.9</t>
+          <t>96552.6462982787</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>857.18</t>
+          <t>104700.006663345</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>702.91</t>
+          <t>128799.043832611</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>570.68</t>
+          <t>174985.628355198</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>452.69</t>
+          <t>226895.335735864</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>341.72</t>
+          <t>285063.894461946</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>264.52</t>
+          <t>326695.747592348</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>173.03</t>
+          <t>424573.448597415</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>230.01</t>
+          <t>286686.34377504</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>668.26</t>
+          <t>63396371020.3545</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>520.85</t>
+          <t>58297306273.7978</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>505.61</t>
+          <t>53519037652.0048</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>651.21</t>
+          <t>73910415449.8846</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1242.29</t>
+          <t>92662979395.4677</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>929.26</t>
+          <t>94746456580.8947</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>761.38</t>
+          <t>82714871428.0554</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>651.81</t>
+          <t>81262626408.2103</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>549.24</t>
+          <t>70563729466.2448</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>438.84</t>
+          <t>67696979757.8175</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>364.85</t>
+          <t>65440769283.7197</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>280.23</t>
+          <t>62569122203.9326</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>222.4</t>
+          <t>53314284111.6087</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>156.14</t>
+          <t>50599978036.8428</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>216.06</t>
+          <t>47294618222.1856</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>311.96</t>
+          <t>64887.0558157066</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>236.64</t>
+          <t>66316.4782153129</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>231.25</t>
+          <t>69744.8129322049</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>290.85</t>
+          <t>63704.5405958984</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>554.75</t>
+          <t>40972.5872294975</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>392.07</t>
+          <t>50383.5503748477</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>321.04</t>
+          <t>59432.2393476032</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>257.03</t>
+          <t>70062.7578836818</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>243.59</t>
+          <t>86035.8176917941</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>179.44</t>
+          <t>108093.675920503</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>137665.432932505</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>103.25</t>
+          <t>177506.771818772</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>83.92</t>
+          <t>241530.294618404</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>52.78</t>
+          <t>322083.959966771</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>90.78</t>
+          <t>216665.457764272</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>600848.033</t>
+          <t>40145839935.1141</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>581454.671</t>
+          <t>39108445716.0178</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>575394.536</t>
+          <t>34215140612.426</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>587968.151</t>
+          <t>35623348700.8714</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>606379.194</t>
+          <t>28701003822.411</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>638951.95</t>
+          <t>37911967909.7854</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>650360.277</t>
+          <t>42216719763.525</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>648851.506</t>
+          <t>47111901947.7279</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>597114.473</t>
+          <t>55591035193.5026</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>638601.477</t>
+          <t>70623830297.3958</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>628598.727</t>
+          <t>87256795585.4532</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>615524.565</t>
+          <t>84995558481.9387</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>583028.342</t>
+          <t>108597153056.324</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>557272.745</t>
+          <t>122622290343.957</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>544992.888</t>
+          <t>124996775462.057</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>410555.117</t>
+          <t>17286.0739059643</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>400576.842</t>
+          <t>23681.312012428</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>397881.719</t>
+          <t>17386.5637549212</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>400702.392</t>
+          <t>27580.5171199825</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>413590.931</t>
+          <t>32638.012392055</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>434436.866</t>
+          <t>48373.3640356883</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>441033.589</t>
+          <t>37120.4069506755</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>439171.665</t>
+          <t>34637.2487796628</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>400560.444</t>
+          <t>42763.2261408171</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>430605.81</t>
+          <t>66891.952434695</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>429825.493</t>
+          <t>89229.9028033591</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>421000.845</t>
+          <t>107557.122643174</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>400454.874</t>
+          <t>85165.4529739441</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>355943.688</t>
+          <t>102489.488630643</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>350163.052</t>
+          <t>70020.8860107671</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>697457.408</t>
+          <t>23250531085.2405</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>685099.595</t>
+          <t>19188860557.78</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>646009.994</t>
+          <t>19303897039.5787</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>639755.017</t>
+          <t>38287066749.0132</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>611208.761</t>
+          <t>63961975573.0566</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>654011.62</t>
+          <t>56834488671.1093</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>674253.18</t>
+          <t>40498151664.5303</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>652181.575</t>
+          <t>34150724460.4823</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>596907.594</t>
+          <t>14972694272.7423</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>626356.353</t>
+          <t>-2926850539.57828</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>611759.613</t>
+          <t>-21816026301.7335</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>585352.967</t>
+          <t>-22426436278.0061</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>567114.859</t>
+          <t>-55282868944.715</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>544534.115</t>
+          <t>-72022312307.1143</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>535024.932</t>
+          <t>-77702157239.8714</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.301</t>
+          <t>184013.03933</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.287</t>
+          <t>225972.00023</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>224582.53112</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.982</t>
+          <t>169713.10346</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>98421.27939</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.996</t>
+          <t>127583.6282</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.985</t>
+          <t>145331.28584</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>163392.52319</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>195083.94397</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>283790.4159</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2.413</t>
+          <t>361659.56723</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2.455</t>
+          <t>455141.0727</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2.811</t>
+          <t>584537.85323</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3.067</t>
+          <t>736187.75332</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.776</t>
+          <t>535212.95726</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>436946.446</t>
+          <t>0.103259296519288</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>415478.922</t>
+          <t>0.0662833215516292</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>398331.132</t>
+          <t>0.0680142813151724</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>397750.215</t>
+          <t>0.0566431202831096</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>408254.988</t>
+          <t>0.0730349963552306</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>429349.784</t>
+          <t>0.0750714831743246</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>430461.746</t>
+          <t>0.0743937179396757</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>424040.774</t>
+          <t>0.0743765234551324</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>385879.583</t>
+          <t>0.076265882939862</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>408673.417</t>
+          <t>0.0917256644846594</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>398879.388</t>
+          <t>0.108278673926384</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>388515.139</t>
+          <t>0.118075484683609</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>365716.564</t>
+          <t>0.111129580886266</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>346895.726</t>
+          <t>0.106788222679935</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>336391.901</t>
+          <t>0.0789405745478521</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.442</t>
+          <t>151159.009193339</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>185338.83086088</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.301</t>
+          <t>184975.256528038</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.232</t>
+          <t>140689.903431833</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>81231.3104575208</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>105661.233291054</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>125423.120332758</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.281</t>
+          <t>147728.913971488</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.352</t>
+          <t>179894.454761889</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>240273.375587034</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.573</t>
+          <t>302330.993567352</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>392153.108558408</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>525840.489767422</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.954</t>
+          <t>674098.379990093</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>510927.635817245</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>52016.337</t>
+          <t>182589.786305454</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>62245.62</t>
+          <t>225627.675546105</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>63873.496</t>
+          <t>226401.480908441</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>51566.752</t>
+          <t>174046.030223463</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>29490.075</t>
+          <t>101732.70129896</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>40138.691</t>
+          <t>132427.198407428</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>49029.692</t>
+          <t>158669.464412438</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>56269.507</t>
+          <t>186418.259328686</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>59463.905</t>
+          <t>230030.513991632</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>76662.074</t>
+          <t>304889.564299288</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>89673.01</t>
+          <t>376391.502262199</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>107953.272</t>
+          <t>488150.895498128</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>121843.213</t>
+          <t>656182.589247839</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>138507.317</t>
+          <t>843107.89603508</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>110954.573</t>
+          <t>637927.263060935</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>689.28</t>
+          <t>698398.796653517</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>543.54</t>
+          <t>1060610.45048632</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>522.92</t>
+          <t>1109586.31399928</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>677.06</t>
+          <t>988657.354094549</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1302.47</t>
+          <t>495139.533299384</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>982.34</t>
+          <t>649222.023518284</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>799.52</t>
+          <t>753625.211715742</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>680.48</t>
+          <t>820040.265349154</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>573.62</t>
+          <t>946943.80952797</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>461.69</t>
+          <t>1214773.63670156</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>379.33</t>
+          <t>1466044.81210744</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>289.98</t>
+          <t>1795955.24022668</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>228.66</t>
+          <t>2368231.30818118</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>156.99</t>
+          <t>3122145.92713759</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>215.59</t>
+          <t>2751483.29982883</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>39.242</t>
+          <t>182589.786305454</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>176888.042554654</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.741</t>
+          <t>176614.705085291</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>36.207</t>
+          <t>159012.398857945</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>61.884</t>
+          <t>174625.742607216</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>51.738</t>
+          <t>189491.669397875</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>43.616</t>
+          <t>204693.723837478</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>38.052</t>
+          <t>216630.729936737</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>237006.684426029</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>23.256</t>
+          <t>245938.142155093</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>18.507</t>
+          <t>253527.634358054</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>14.004</t>
+          <t>275247.882622828</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>10.287</t>
+          <t>306523.431048749</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>7.803</t>
+          <t>323306.311472351</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>9.971</t>
+          <t>293684.452293807</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>151159.009193339</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>144734.068052945</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>143148.986051173</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>126820.233035736</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>138527.180245978</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>149807.452802791</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>159931.278700196</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>168880.052620492</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>180965.307474259</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>188910.501957567</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>196635.328636788</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>212952.435282937</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>236778.050279621</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>248468.088437632</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>226070.483272918</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>132438.202244546</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>149611.154263895</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>156210.014811559</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>129431.994136537</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>75058.4446510402</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>100155.043572572</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>115081.828257562</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>125299.006061314</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>148773.334538368</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>210858.263360713</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>278393.174907801</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>357415.364121872</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>458129.939002161</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>585275.371534919</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>443450.474779065</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>410555116653.145</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>400576841510.435</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>397881718733.923</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>400702392074.341</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>413590930911.26</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>434436866290.052</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>441033589257.944</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>439171664536.815</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>400560443733.551</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>430605810476.65</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>429825493314.13</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>421000844906.613</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>400454873966.32</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>355943688068.631</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>350163052186.907</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>600848032951.605</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>581454671158.324</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>575394536316.224</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>587968151291.057</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>606379193698.521</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>638951950352.549</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>650360277317.857</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>648851506246.042</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>597114472965.914</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>638601476869.193</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>628598727425.933</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>615524565064.372</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>583028341695.551</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>557272744820.623</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>544992887562.261</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>436946446291.871</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>415478922343.414</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>398331132362.087</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>397750215020.591</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>408254987715.936</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>429349784326.5</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>430461745863.206</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>424040773690.563</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>385879583108.403</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>408673417262.61</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>398879387858.787</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>388515138964.496</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>365716564081.767</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>346895725701.889</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>336391900517.481</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>75064020.4105068</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>72952323.1444098</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>72751632.044012</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>70678642.9778868</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>72536304.6533051</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>73725622.6407169</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>74726901.7613503</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>74927528.6053486</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>75795783.2238575</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>76274192.8802783</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>76903373.2930301</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>77376240.0225884</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>78351850.9170373</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>78687685.7840791</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>75717000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>64260852.7275049</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>62370125.243572</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>62200950.4041932</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>59853721.200772</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>60787342.1386412</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>61691101.5357199</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>62297793.6298094</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>62039441.3470101</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>62159453.1953076</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>62522331.8698624</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>63551338.8363913</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>63927636.7601688</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>64757004.4029572</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>64970283.6939326</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>62523399.1033319</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>147480245205.283</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>145736147183.706</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>143947992992.623</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>139814022951.23</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>140635671978.995</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>142066304119.395</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>143725423376.037</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>144652032453.852</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>145979322680.39</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>147237003746.657</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>147629163489.76</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>148512152853.828</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>150394470761.21</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>151060450175.413</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>147091434048</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>120664856778.547</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>119341921117.83</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>118011107599.581</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>113027023673.612</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>113179630388.439</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>113940226544.234</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>114153881417.255</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>113749879436.617</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>112966140149.546</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>114564730880.348</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>116454543903.835</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>117538536852.503</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>119035202129.533</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>111132000708.532</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>108212078898.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.182644137456708</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.182644137456708</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.182644137456708</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.182644137456708</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.186392000176828</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.190853502739363</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.197418348447124</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.201371650735483</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.20590896260967</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.208463226741578</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.213949348034136</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.213949348034136</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.213949348034136</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.213949348034136</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.213949348034136</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.723675629110238</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.723675629110238</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.723675629110238</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.723675629110238</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.720836831233209</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.717701641385584</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.715688374619273</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.713068185136395</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.713219656479643</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.715184419634513</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.712203752107516</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.712203752107516</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.712203752107516</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.712203752107516</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.712203752107516</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0651088048616247</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0651088048616247</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0651088048616247</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0651088048616247</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0641997400185345</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0628734273036245</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0583218483621743</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.056988735556694</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0522999523392593</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0477809250524804</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0452754712869191</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0452754712869191</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0452754712869191</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0452754712869191</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0452754712869191</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.186189205710391</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.188273300426507</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.189759162992788</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.192639456044557</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.197085712200554</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.202813144213498</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.206031707997566</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.212801510068767</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.216394202215119</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.219585169959055</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.222311790407097</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.222079204426501</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.21956996313441</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.218172980030862</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.220413903743844</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.754175230091266</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.751558994555753</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.750231024341683</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.748722733810512</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.745448012458926</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.741960586816535</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.740369533550678</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.734947228636935</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.731183627120109</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.731145168907696</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.729135516660194</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.72875342047666</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.729957904978536</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.730416641995585</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.728323186282626</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0310641356269143</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0315962764463119</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0314383840941004</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0300663815735025</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0288948467690914</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.026654840398538</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0250273298803271</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0236798327228689</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0238507420933425</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0206982325618201</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0199812643612804</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0205959465254105</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0219007033156253</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0228389494021241</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0226914814021017</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>611082.02965</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>742843.07242</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>748922.56241</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>585286.09149</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>338189.43534</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>446231.10885</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>546151.61426</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>607506.03292</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>758702.71939</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1023619.55126</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1309048.53101</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1701038.34165</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2259263.42913</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2891627.874</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2185970.42952</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>315027.98855</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>375238.82981</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>382611.49572</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>303478.02436</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>176791.14595</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>232582.24198</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>273751.29267</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>311717.26539</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>378803.84853</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>515747.82766</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>654784.67717</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>845566.25962</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1114312.52825</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1428383.26757</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1081377.73784</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3183511.61798828</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3249229.60353332</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3286038.23799151</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3285388.05780873</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3298508.07812258</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>3343495.03284285</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3426089.69794493</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>3508315.79941189</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3625294.32007167</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3768869.42000662</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3930747.73027342</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>4140686.69037268</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>4425090.00828151</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>4740768.11278896</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>4951947.44131607</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
